--- a/Excel/LegacyConfig.xlsx
+++ b/Excel/LegacyConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="69">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
@@ -38,19 +41,25 @@
     <t>ItemId</t>
   </si>
   <si>
+    <t>StartLevel</t>
+  </si>
+  <si>
+    <t>EndLevel</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
-    <t>AttrIdList</t>
-  </si>
-  <si>
-    <t>AttrValueList</t>
-  </si>
-  <si>
-    <t>AttrRiseList</t>
-  </si>
-  <si>
-    <t>LayerIdList</t>
+    <t>AtrIdList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
+  </si>
+  <si>
+    <t>AtrRiseList</t>
+  </si>
+  <si>
+    <t>LevelIdList</t>
   </si>
   <si>
     <t>LayerValueList</t>
@@ -59,13 +68,13 @@
     <t>LayerRiseList</t>
   </si>
   <si>
-    <t>PowerList</t>
-  </si>
-  <si>
-    <t>DropRate</t>
-  </si>
-  <si>
-    <t>RecoveryNubmer</t>
+    <t>SpeAtrList</t>
+  </si>
+  <si>
+    <t>SpeVueList</t>
+  </si>
+  <si>
+    <t>SpeLevel</t>
   </si>
   <si>
     <t>Id</t>
@@ -80,70 +89,100 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>long[]</t>
+  </si>
+  <si>
     <t>传世战刃</t>
   </si>
   <si>
-    <t>14,16,15,26</t>
-  </si>
-  <si>
-    <t>100,100,100,100</t>
-  </si>
-  <si>
-    <t>33,2004,2007,2011</t>
-  </si>
-  <si>
-    <t>10,2,2,1</t>
-  </si>
-  <si>
-    <t>100,0,0</t>
+    <t>1001,1002,1004</t>
+  </si>
+  <si>
+    <t>5,2,5</t>
+  </si>
+  <si>
+    <t>1,2,4</t>
+  </si>
+  <si>
+    <t>100,5,10</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>攻速</t>
   </si>
   <si>
     <t>传世战甲</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>抗暴率</t>
+  </si>
+  <si>
     <t>传世战链</t>
   </si>
   <si>
-    <t>50,50,50,50</t>
-  </si>
-  <si>
-    <t>33,2004,2007,2002</t>
-  </si>
-  <si>
-    <t>5,1,1,1</t>
-  </si>
-  <si>
-    <t>30,10,10</t>
+    <t>13</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>命中</t>
   </si>
   <si>
     <t>传世战盔</t>
   </si>
   <si>
-    <t>33,2004,2007,2003</t>
+    <t>14</t>
+  </si>
+  <si>
+    <t>闪避</t>
   </si>
   <si>
     <t>传世战镯</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>传世战戒</t>
   </si>
   <si>
     <t>传世战带</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
     <t>传世战靴</t>
   </si>
   <si>
     <t>传世法杖</t>
   </si>
   <si>
-    <t>14,16,15,27</t>
-  </si>
-  <si>
-    <t>34,2005,2008,2011</t>
-  </si>
-  <si>
-    <t>0,100,0</t>
+    <t>1001,1002,1005</t>
+  </si>
+  <si>
+    <t>1,2,5</t>
+  </si>
+  <si>
+    <t>移速</t>
   </si>
   <si>
     <t>传世法衣</t>
@@ -152,18 +191,9 @@
     <t>传世法链</t>
   </si>
   <si>
-    <t>34,2005,2008,2002</t>
-  </si>
-  <si>
-    <t>10,30,10</t>
-  </si>
-  <si>
     <t>传世法帽</t>
   </si>
   <si>
-    <t>34,2005,2008,2003</t>
-  </si>
-  <si>
     <t>传世法镯</t>
   </si>
   <si>
@@ -179,13 +209,10 @@
     <t>传世道剑</t>
   </si>
   <si>
-    <t>14,16,15,28</t>
-  </si>
-  <si>
-    <t>35,2006,2009,2011</t>
-  </si>
-  <si>
-    <t>0,0,100</t>
+    <t>1001,1002,1006</t>
+  </si>
+  <si>
+    <t>1,2,6</t>
   </si>
   <si>
     <t>传世道袍</t>
@@ -194,16 +221,7 @@
     <t>传世道链</t>
   </si>
   <si>
-    <t>35,2006,2009,2002</t>
-  </si>
-  <si>
-    <t>10,10,30</t>
-  </si>
-  <si>
     <t>传世道冠</t>
-  </si>
-  <si>
-    <t>35,2006,2009,2003</t>
   </si>
   <si>
     <t>传世道镯</t>
@@ -228,7 +246,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,13 +266,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -725,144 +736,150 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1183,1168 +1200,1298 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="5" width="9.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="2" customWidth="1"/>
-    <col min="9" max="10" width="15.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.125" style="2" customWidth="1"/>
-    <col min="13" max="15" width="12.125" style="1" customWidth="1"/>
-    <col min="16" max="16371" width="9" style="2"/>
-    <col min="16372" max="16384" width="9" style="1"/>
+    <col min="6" max="7" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
+    <col min="11" max="12" width="15.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="13.375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="21.5" style="3" customWidth="1"/>
+    <col min="16" max="16" width="20.6666666666667" style="3" customWidth="1"/>
+    <col min="17" max="17" width="19.8333333333333" style="3" customWidth="1"/>
+    <col min="18" max="18" width="10.5" style="4" customWidth="1"/>
+    <col min="19" max="16367" width="9" style="2"/>
+    <col min="16368" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="I3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="J3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="K3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="3" t="s">
+      <c r="L3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="N3" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="1">
         <v>6000001</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="5" t="s">
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="5" t="s">
+      <c r="I6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="1">
-        <v>20</v>
-      </c>
-      <c r="O6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="J6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="1">
         <v>6000002</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="5" t="s">
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="1">
-        <v>20</v>
-      </c>
-      <c r="O7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="J7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="1">
         <v>6000003</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="7">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="N8" s="1">
-        <v>100</v>
-      </c>
-      <c r="O8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="R8" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="1">
         <v>6000003</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="5" t="s">
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="N9" s="1">
-        <v>100</v>
-      </c>
-      <c r="O9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="R9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="1">
         <v>6000003</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="5" t="s">
+      <c r="F10" s="7">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="N10" s="1">
-        <v>100</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="R10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="1">
         <v>6000003</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="5" t="s">
+      <c r="F11" s="7">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="N11" s="1">
-        <v>100</v>
-      </c>
-      <c r="O11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="1">
         <v>6000003</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="5" t="s">
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="N12" s="1">
-        <v>100</v>
-      </c>
-      <c r="O12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="R12" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="1">
         <v>6000003</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" s="5" t="s">
+      <c r="F13" s="7">
+        <v>1</v>
+      </c>
+      <c r="G13" s="7">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="N13" s="1">
-        <v>100</v>
-      </c>
-      <c r="O13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="R13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="O14" s="8"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C15" s="1">
         <v>9</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="1">
         <v>6000003</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N15" s="1">
-        <v>20</v>
-      </c>
-      <c r="O15" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F15" s="7">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="8"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C16" s="1">
         <v>10</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="1">
         <v>6000003</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N16" s="1">
-        <v>20</v>
-      </c>
-      <c r="O16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F16" s="7">
+        <v>1</v>
+      </c>
+      <c r="G16" s="7">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C17" s="1">
         <v>11</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="1">
         <v>6000003</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N17" s="1">
-        <v>100</v>
-      </c>
-      <c r="O17" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C18" s="1">
         <v>12</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="1">
         <v>6000003</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N18" s="1">
-        <v>100</v>
-      </c>
-      <c r="O18" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F18" s="7">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C19" s="1">
         <v>13</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="1">
         <v>6000003</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N19" s="1">
-        <v>100</v>
-      </c>
-      <c r="O19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F19" s="7">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C20" s="1">
         <v>14</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="1">
         <v>6000003</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N20" s="1">
-        <v>100</v>
-      </c>
-      <c r="O20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F20" s="7">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C21" s="1">
         <v>15</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="1">
         <v>6000003</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N21" s="1">
-        <v>100</v>
-      </c>
-      <c r="O21" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F21" s="7">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C22" s="1">
         <v>16</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="1">
         <v>6000003</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N22" s="1">
-        <v>100</v>
-      </c>
-      <c r="O22" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F22" s="7">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C24" s="1">
         <v>17</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="1">
         <v>6000003</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N24" s="1">
-        <v>20</v>
-      </c>
-      <c r="O24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F24" s="7">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C25" s="1">
         <v>18</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="1">
         <v>6000003</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N25" s="1">
-        <v>20</v>
-      </c>
-      <c r="O25" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F25" s="7">
+        <v>1</v>
+      </c>
+      <c r="G25" s="7">
+        <v>10</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C26" s="1">
         <v>19</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="1">
         <v>6000003</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N26" s="1">
-        <v>100</v>
-      </c>
-      <c r="O26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F26" s="7">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C27" s="1">
         <v>20</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="1">
         <v>6000003</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N27" s="1">
-        <v>100</v>
-      </c>
-      <c r="O27" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F27" s="7">
+        <v>1</v>
+      </c>
+      <c r="G27" s="7">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C28" s="1">
         <v>21</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="1">
         <v>6000003</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N28" s="1">
-        <v>100</v>
-      </c>
-      <c r="O28" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F28" s="7">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="4"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C29" s="1">
         <v>22</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="1">
         <v>6000003</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="7">
+        <v>1</v>
+      </c>
+      <c r="G29" s="7">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N29" s="1">
-        <v>100</v>
-      </c>
-      <c r="O29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="J29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C30" s="1">
         <v>23</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="1">
         <v>6000003</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="7">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N30" s="1">
-        <v>100</v>
-      </c>
-      <c r="O30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="M30" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C31" s="1">
         <v>24</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="1">
         <v>6000003</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N31" s="1">
-        <v>100</v>
-      </c>
-      <c r="O31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E32" s="4"/>
+      <c r="F31" s="7">
+        <v>1</v>
+      </c>
+      <c r="G31" s="7">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="4"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 J3 K3 L3 M3 N3 O3 D4 E4 F4 G4 H4 I4 J4 K4 L4 M4 N4 O4 D5 E5 F5 G5 H5 I5 J5 K5 L5 M5 N5 O5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 G3 H3:K3 C4:E4 F4 G4 H4 I4 J4 K4 C5:E5 F5 G5 H5:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/LegacyConfig.xlsx
+++ b/Excel/LegacyConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Role</t>
   </si>
   <si>
+    <t>Part</t>
+  </si>
+  <si>
     <t>ItemId</t>
   </si>
   <si>
@@ -56,30 +59,39 @@
     <t>AtrVueList</t>
   </si>
   <si>
-    <t>AtrRiseList</t>
-  </si>
-  <si>
     <t>LevelIdList</t>
   </si>
   <si>
+    <t>LevelValueList</t>
+  </si>
+  <si>
+    <t>LayerIdList</t>
+  </si>
+  <si>
+    <t>LayerVueList</t>
+  </si>
+  <si>
+    <t>SpeAtrList</t>
+  </si>
+  <si>
+    <t>SpeVueList</t>
+  </si>
+  <si>
+    <t>SpeLevel</t>
+  </si>
+  <si>
+    <t>Fee1</t>
+  </si>
+  <si>
+    <t>Fee2</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
     <t>LayerValueList</t>
   </si>
   <si>
-    <t>LayerRiseList</t>
-  </si>
-  <si>
-    <t>SpeAtrList</t>
-  </si>
-  <si>
-    <t>SpeVueList</t>
-  </si>
-  <si>
-    <t>SpeLevel</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -90,6 +102,9 @@
   </si>
   <si>
     <t>long[]</t>
+  </si>
+  <si>
+    <t>long</t>
   </si>
   <si>
     <t>传世战刃</t>
@@ -866,7 +881,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -879,7 +894,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1200,60 +1214,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="5" width="9.875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
-    <col min="11" max="12" width="15.625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="13.375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="21.5" style="3" customWidth="1"/>
-    <col min="16" max="16" width="20.6666666666667" style="3" customWidth="1"/>
-    <col min="17" max="17" width="19.8333333333333" style="3" customWidth="1"/>
-    <col min="18" max="18" width="10.5" style="4" customWidth="1"/>
-    <col min="19" max="16367" width="9" style="2"/>
-    <col min="16368" max="16384" width="9" style="1"/>
+    <col min="3" max="6" width="9.875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.625" style="2" customWidth="1"/>
+    <col min="13" max="14" width="13.375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13" style="3" customWidth="1"/>
+    <col min="17" max="17" width="12" style="3" customWidth="1"/>
+    <col min="18" max="18" width="10.4166666666667" style="3" customWidth="1"/>
+    <col min="19" max="20" width="11.75" style="3" customWidth="1"/>
+    <col min="21" max="21" width="10.5" style="4" customWidth="1"/>
+    <col min="22" max="16370" width="9" style="2"/>
+    <col min="16371" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
-      <c r="O1" s="3"/>
+      <c r="O1" s="2"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="3"/>
+      <c r="O2" s="2"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -1292,7 +1311,7 @@
       <c r="N3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="P3" s="6" t="s">
@@ -1301,13 +1320,22 @@
       <c r="Q3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="6"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>2</v>
@@ -1337,12 +1365,12 @@
         <v>10</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="P4" s="6" t="s">
@@ -1351,59 +1379,77 @@
       <c r="Q4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R4" s="6"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="U4" s="6"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R5" s="6"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:18">
+        <v>24</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="U5" s="6"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1411,49 +1457,58 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
         <v>6000001</v>
       </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
       <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
         <v>10</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="9" t="s">
+      <c r="I6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="K6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="L6" s="8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="M6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T6" s="1">
+        <v>100</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1461,49 +1516,58 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
         <v>6000002</v>
       </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
       <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
         <v>10</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="P7" s="9" t="s">
+      <c r="I7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q7" s="9" t="s">
+      <c r="K7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="L7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q7" s="8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S7" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T7" s="1">
+        <v>100</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1511,49 +1575,58 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1">
         <v>6000003</v>
       </c>
-      <c r="F8" s="7">
-        <v>1</v>
-      </c>
       <c r="G8" s="7">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7">
         <v>10</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="S8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T8" s="1">
+        <v>100</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1561,49 +1634,58 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1">
         <v>6000003</v>
       </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
       <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
         <v>10</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q9" s="9" t="s">
+      <c r="I9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="R9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="L9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T9" s="1">
+        <v>100</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1611,49 +1693,58 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1">
         <v>6000003</v>
       </c>
-      <c r="F10" s="7">
-        <v>1</v>
-      </c>
       <c r="G10" s="7">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7">
         <v>10</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T10" s="1">
+        <v>100</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1661,46 +1752,55 @@
         <v>1</v>
       </c>
       <c r="E11" s="1">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1">
         <v>6000003</v>
       </c>
-      <c r="F11" s="7">
-        <v>1</v>
-      </c>
       <c r="G11" s="7">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7">
         <v>10</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q11" s="9" t="s">
+      <c r="I11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="L11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S11" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1708,49 +1808,58 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1">
         <v>6000003</v>
       </c>
-      <c r="F12" s="7">
-        <v>1</v>
-      </c>
       <c r="G12" s="7">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7">
         <v>10</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q12" s="9" t="s">
+      <c r="I12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="R12" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="L12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S12" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T12" s="1">
+        <v>100</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1758,52 +1867,59 @@
         <v>1</v>
       </c>
       <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1">
         <v>6000003</v>
       </c>
-      <c r="F13" s="7">
-        <v>1</v>
-      </c>
       <c r="G13" s="7">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7">
         <v>10</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q13" s="9" t="s">
+      <c r="I13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="R13" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="O14" s="8"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="L13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T13" s="1">
+        <v>100</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1"/>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C15" s="1">
         <v>9</v>
       </c>
@@ -1811,43 +1927,58 @@
         <v>2</v>
       </c>
       <c r="E15" s="1">
+        <v>9</v>
+      </c>
+      <c r="F15" s="1">
         <v>6000003</v>
       </c>
-      <c r="F15" s="7">
-        <v>1</v>
-      </c>
       <c r="G15" s="7">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7">
         <v>10</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="I15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S15" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T15" s="1">
+        <v>100</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="C16" s="1">
         <v>10</v>
       </c>
@@ -1855,41 +1986,56 @@
         <v>2</v>
       </c>
       <c r="E16" s="1">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1">
         <v>6000003</v>
       </c>
-      <c r="F16" s="7">
-        <v>1</v>
-      </c>
       <c r="G16" s="7">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7">
         <v>10</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="I16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S16" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T16" s="1">
+        <v>100</v>
+      </c>
+      <c r="U16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C17" s="1">
         <v>11</v>
       </c>
@@ -1897,41 +2043,56 @@
         <v>2</v>
       </c>
       <c r="E17" s="1">
+        <v>11</v>
+      </c>
+      <c r="F17" s="1">
         <v>6000003</v>
       </c>
-      <c r="F17" s="7">
-        <v>1</v>
-      </c>
       <c r="G17" s="7">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7">
         <v>10</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="I17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S17" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T17" s="1">
+        <v>100</v>
+      </c>
+      <c r="U17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C18" s="1">
         <v>12</v>
       </c>
@@ -1939,41 +2100,56 @@
         <v>2</v>
       </c>
       <c r="E18" s="1">
+        <v>12</v>
+      </c>
+      <c r="F18" s="1">
         <v>6000003</v>
       </c>
-      <c r="F18" s="7">
-        <v>1</v>
-      </c>
       <c r="G18" s="7">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7">
         <v>10</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="K18" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S18" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T18" s="1">
+        <v>100</v>
+      </c>
+      <c r="U18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C19" s="1">
         <v>13</v>
       </c>
@@ -1981,41 +2157,56 @@
         <v>2</v>
       </c>
       <c r="E19" s="1">
+        <v>13</v>
+      </c>
+      <c r="F19" s="1">
         <v>6000003</v>
       </c>
-      <c r="F19" s="7">
-        <v>1</v>
-      </c>
       <c r="G19" s="7">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7">
         <v>10</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I19" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S19" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T19" s="1">
+        <v>100</v>
+      </c>
+      <c r="U19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C20" s="1">
         <v>14</v>
       </c>
@@ -2023,41 +2214,56 @@
         <v>2</v>
       </c>
       <c r="E20" s="1">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1">
         <v>6000003</v>
       </c>
-      <c r="F20" s="7">
-        <v>1</v>
-      </c>
       <c r="G20" s="7">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7">
         <v>10</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="I20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S20" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T20" s="1">
+        <v>100</v>
+      </c>
+      <c r="U20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C21" s="1">
         <v>15</v>
       </c>
@@ -2065,41 +2271,56 @@
         <v>2</v>
       </c>
       <c r="E21" s="1">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1">
         <v>6000003</v>
       </c>
-      <c r="F21" s="7">
-        <v>1</v>
-      </c>
       <c r="G21" s="7">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7">
         <v>10</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="9" t="s">
+      <c r="Q21" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="M21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S21" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T21" s="1">
+        <v>100</v>
+      </c>
+      <c r="U21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C22" s="1">
         <v>16</v>
       </c>
@@ -2107,47 +2328,64 @@
         <v>2</v>
       </c>
       <c r="E22" s="1">
+        <v>16</v>
+      </c>
+      <c r="F22" s="1">
         <v>6000003</v>
       </c>
-      <c r="F22" s="7">
-        <v>1</v>
-      </c>
       <c r="G22" s="7">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7">
         <v>10</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="9" t="s">
+      <c r="Q22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="4"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="O23" s="3"/>
+      <c r="R22" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S22" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T22" s="1">
+        <v>100</v>
+      </c>
+      <c r="U22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
-      <c r="R23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C24" s="1">
         <v>17</v>
       </c>
@@ -2155,41 +2393,56 @@
         <v>3</v>
       </c>
       <c r="E24" s="1">
+        <v>17</v>
+      </c>
+      <c r="F24" s="1">
         <v>6000003</v>
       </c>
-      <c r="F24" s="7">
-        <v>1</v>
-      </c>
       <c r="G24" s="7">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7">
         <v>10</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="4"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="I24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S24" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T24" s="1">
+        <v>100</v>
+      </c>
+      <c r="U24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C25" s="1">
         <v>18</v>
       </c>
@@ -2197,41 +2450,56 @@
         <v>3</v>
       </c>
       <c r="E25" s="1">
+        <v>18</v>
+      </c>
+      <c r="F25" s="1">
         <v>6000003</v>
       </c>
-      <c r="F25" s="7">
-        <v>1</v>
-      </c>
       <c r="G25" s="7">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7">
         <v>10</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="I25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S25" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T25" s="1">
+        <v>100</v>
+      </c>
+      <c r="U25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C26" s="1">
         <v>19</v>
       </c>
@@ -2239,41 +2507,56 @@
         <v>3</v>
       </c>
       <c r="E26" s="1">
+        <v>19</v>
+      </c>
+      <c r="F26" s="1">
         <v>6000003</v>
       </c>
-      <c r="F26" s="7">
-        <v>1</v>
-      </c>
       <c r="G26" s="7">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7">
         <v>10</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="I26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S26" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T26" s="1">
+        <v>100</v>
+      </c>
+      <c r="U26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C27" s="1">
         <v>20</v>
       </c>
@@ -2281,41 +2564,56 @@
         <v>3</v>
       </c>
       <c r="E27" s="1">
+        <v>20</v>
+      </c>
+      <c r="F27" s="1">
         <v>6000003</v>
       </c>
-      <c r="F27" s="7">
-        <v>1</v>
-      </c>
       <c r="G27" s="7">
+        <v>1</v>
+      </c>
+      <c r="H27" s="7">
         <v>10</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="I27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S27" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T27" s="1">
+        <v>100</v>
+      </c>
+      <c r="U27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C28" s="1">
         <v>21</v>
       </c>
@@ -2323,41 +2621,56 @@
         <v>3</v>
       </c>
       <c r="E28" s="1">
+        <v>21</v>
+      </c>
+      <c r="F28" s="1">
         <v>6000003</v>
       </c>
-      <c r="F28" s="7">
-        <v>1</v>
-      </c>
       <c r="G28" s="7">
+        <v>1</v>
+      </c>
+      <c r="H28" s="7">
         <v>10</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="K28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S28" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T28" s="1">
+        <v>100</v>
+      </c>
+      <c r="U28" s="4"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C29" s="1">
         <v>22</v>
       </c>
@@ -2365,41 +2678,56 @@
         <v>3</v>
       </c>
       <c r="E29" s="1">
+        <v>22</v>
+      </c>
+      <c r="F29" s="1">
         <v>6000003</v>
       </c>
-      <c r="F29" s="7">
-        <v>1</v>
-      </c>
       <c r="G29" s="7">
+        <v>1</v>
+      </c>
+      <c r="H29" s="7">
         <v>10</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="I29" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="M29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S29" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T29" s="1">
+        <v>100</v>
+      </c>
+      <c r="U29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C30" s="1">
         <v>23</v>
       </c>
@@ -2407,41 +2735,56 @@
         <v>3</v>
       </c>
       <c r="E30" s="1">
+        <v>23</v>
+      </c>
+      <c r="F30" s="1">
         <v>6000003</v>
       </c>
-      <c r="F30" s="7">
-        <v>1</v>
-      </c>
       <c r="G30" s="7">
+        <v>1</v>
+      </c>
+      <c r="H30" s="7">
         <v>10</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="4"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="I30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P30" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S30" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T30" s="1">
+        <v>100</v>
+      </c>
+      <c r="U30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="C31" s="1">
         <v>24</v>
       </c>
@@ -2449,49 +2792,66 @@
         <v>3</v>
       </c>
       <c r="E31" s="1">
+        <v>24</v>
+      </c>
+      <c r="F31" s="1">
         <v>6000003</v>
       </c>
-      <c r="F31" s="7">
-        <v>1</v>
-      </c>
       <c r="G31" s="7">
+        <v>1</v>
+      </c>
+      <c r="H31" s="7">
         <v>10</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="4"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="O32" s="3"/>
+      <c r="I31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q31" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S31" s="1">
+        <v>10000</v>
+      </c>
+      <c r="T31" s="1">
+        <v>100</v>
+      </c>
+      <c r="U31" s="4"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:21">
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
-      <c r="R32" s="4"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 G3 H3:K3 C4:E4 F4 G4 H4 I4 J4 K4 C5:E5 F5 G5 H5:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/LegacyConfig.xlsx
+++ b/Excel/LegacyConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="87">
   <si>
     <t>#</t>
   </si>
@@ -59,24 +59,24 @@
     <t>AtrVueList</t>
   </si>
   <si>
+    <t>SpeIdList</t>
+  </si>
+  <si>
+    <t>SpeVueList</t>
+  </si>
+  <si>
+    <t>SpeLayerList</t>
+  </si>
+  <si>
     <t>LevelIdList</t>
   </si>
   <si>
     <t>LevelValueList</t>
   </si>
   <si>
-    <t>LayerIdList</t>
-  </si>
-  <si>
-    <t>LayerVueList</t>
-  </si>
-  <si>
     <t>SpeAtrList</t>
   </si>
   <si>
-    <t>SpeVueList</t>
-  </si>
-  <si>
     <t>SpeLevel</t>
   </si>
   <si>
@@ -89,9 +89,6 @@
     <t>Id</t>
   </si>
   <si>
-    <t>LayerValueList</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -110,105 +107,132 @@
     <t>传世战刃</t>
   </si>
   <si>
-    <t>1001,1002,1004</t>
-  </si>
-  <si>
-    <t>5,2,5</t>
-  </si>
-  <si>
-    <t>1,2,4</t>
-  </si>
-  <si>
-    <t>100,5,10</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>3,1004</t>
+  </si>
+  <si>
+    <t>200,5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>1003,4</t>
+  </si>
+  <si>
+    <t>5,200</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>攻速</t>
-  </si>
-  <si>
     <t>传世战甲</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>抗暴率</t>
+    <t>2,1004</t>
+  </si>
+  <si>
+    <t>1002,4</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>传世战链</t>
   </si>
   <si>
+    <t>100,2</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2,100</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>命中</t>
-  </si>
-  <si>
     <t>传世战盔</t>
   </si>
   <si>
+    <t>1,1004</t>
+  </si>
+  <si>
+    <t>2000,2</t>
+  </si>
+  <si>
+    <t>1001,4</t>
+  </si>
+  <si>
+    <t>5,100</t>
+  </si>
+  <si>
     <t>14</t>
   </si>
   <si>
-    <t>闪避</t>
-  </si>
-  <si>
     <t>传世战镯</t>
   </si>
   <si>
-    <t>11</t>
+    <t>22</t>
   </si>
   <si>
     <t>传世战戒</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>传世战带</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>爆伤</t>
+    <t>27</t>
   </si>
   <si>
     <t>传世战靴</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>传世法杖</t>
   </si>
   <si>
-    <t>1001,1002,1005</t>
-  </si>
-  <si>
-    <t>1,2,5</t>
-  </si>
-  <si>
-    <t>移速</t>
+    <t>3,1005</t>
+  </si>
+  <si>
+    <t>1003,5</t>
   </si>
   <si>
     <t>传世法衣</t>
   </si>
   <si>
+    <t>2,1005</t>
+  </si>
+  <si>
+    <t>1002,5</t>
+  </si>
+  <si>
     <t>传世法链</t>
   </si>
   <si>
     <t>传世法帽</t>
   </si>
   <si>
+    <t>1,1005</t>
+  </si>
+  <si>
+    <t>1001,5</t>
+  </si>
+  <si>
     <t>传世法镯</t>
   </si>
   <si>
@@ -224,19 +248,34 @@
     <t>传世道剑</t>
   </si>
   <si>
-    <t>1001,1002,1006</t>
-  </si>
-  <si>
-    <t>1,2,6</t>
+    <t>3,1006</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1003,6</t>
   </si>
   <si>
     <t>传世道袍</t>
   </si>
   <si>
+    <t>2,1006</t>
+  </si>
+  <si>
+    <t>1002,6</t>
+  </si>
+  <si>
     <t>传世道链</t>
   </si>
   <si>
     <t>传世道冠</t>
+  </si>
+  <si>
+    <t>1,1006</t>
+  </si>
+  <si>
+    <t>1001,6</t>
   </si>
   <si>
     <t>传世道镯</t>
@@ -1214,7 +1253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1224,19 +1263,20 @@
     <col min="9" max="9" width="12.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="13.375" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="2" customWidth="1"/>
-    <col min="13" max="14" width="13.375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13" style="3" customWidth="1"/>
-    <col min="17" max="17" width="12" style="3" customWidth="1"/>
-    <col min="18" max="18" width="10.4166666666667" style="3" customWidth="1"/>
-    <col min="19" max="20" width="11.75" style="3" customWidth="1"/>
-    <col min="21" max="21" width="10.5" style="4" customWidth="1"/>
-    <col min="22" max="16370" width="9" style="2"/>
-    <col min="16371" max="16384" width="9" style="1"/>
+    <col min="12" max="12" width="13.375" style="2" customWidth="1"/>
+    <col min="13" max="14" width="11.125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="15.625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13.375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="13" style="3" customWidth="1"/>
+    <col min="18" max="18" width="12" style="3" customWidth="1"/>
+    <col min="19" max="19" width="10.4166666666667" style="3" customWidth="1"/>
+    <col min="20" max="21" width="11.75" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.5" style="4" customWidth="1"/>
+    <col min="23" max="16371" width="9" style="2"/>
+    <col min="16372" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:21">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="J1" s="2"/>
@@ -1245,16 +1285,17 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="P1" s="3"/>
+      <c r="P1" s="2"/>
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="3"/>
+      <c r="V1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:21">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="J2" s="2"/>
@@ -1263,16 +1304,17 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="3"/>
+      <c r="P2" s="2"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="3"/>
+      <c r="V2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:21">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -1314,24 +1356,27 @@
       <c r="O3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="R3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="S3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="6"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="V3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
@@ -1365,7 +1410,7 @@
         <v>10</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>12</v>
@@ -1373,83 +1418,89 @@
       <c r="O4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="R4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="S4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="T4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="6"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="V4" s="6"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="K5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>23</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="U5" s="6"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:21">
+        <v>24</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="6"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1469,22 +1520,22 @@
         <v>10</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>30</v>
+      <c r="N6" s="1">
+        <v>10</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>30</v>
@@ -1498,17 +1549,17 @@
       <c r="R6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" s="1">
         <v>10000</v>
       </c>
-      <c r="T6" s="1">
+      <c r="U6" s="1">
         <v>100</v>
       </c>
-      <c r="U6" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:21">
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1531,43 +1582,43 @@
         <v>35</v>
       </c>
       <c r="J7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="M7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>30</v>
+      <c r="N7" s="1">
+        <v>10</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S7" s="1">
+      <c r="S7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T7" s="1">
         <v>10000</v>
       </c>
-      <c r="T7" s="1">
+      <c r="U7" s="1">
         <v>100</v>
       </c>
-      <c r="U7" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:21">
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1587,46 +1638,46 @@
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="M8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N8" s="1">
+        <v>10</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>30</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S8" s="1">
+      <c r="S8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T8" s="1">
         <v>10000</v>
       </c>
-      <c r="T8" s="1">
+      <c r="U8" s="1">
         <v>100</v>
       </c>
-      <c r="U8" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:21">
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1646,46 +1697,46 @@
         <v>10</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="K9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="M9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N9" s="1">
+        <v>10</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="R9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S9" s="1">
+      <c r="S9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T9" s="1">
         <v>10000</v>
       </c>
-      <c r="T9" s="1">
+      <c r="U9" s="1">
         <v>100</v>
       </c>
-      <c r="U9" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:21">
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1705,46 +1756,46 @@
         <v>10</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="K10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="M10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N10" s="1">
+        <v>10</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="R10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T10" s="1">
         <v>10000</v>
       </c>
-      <c r="T10" s="1">
+      <c r="U10" s="1">
         <v>100</v>
       </c>
-      <c r="U10" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:21">
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1764,43 +1815,46 @@
         <v>10</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="M11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N11" s="1">
+        <v>10</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>30</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="R11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T11" s="1">
         <v>10000</v>
       </c>
-      <c r="T11" s="1">
+      <c r="U11" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:21">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1820,46 +1874,46 @@
         <v>10</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="K12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="M12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N12" s="1">
+        <v>10</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="R12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T12" s="1">
         <v>10000</v>
       </c>
-      <c r="T12" s="1">
+      <c r="U12" s="1">
         <v>100</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:21">
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1879,47 +1933,47 @@
         <v>10</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="K13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="M13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N13" s="1">
+        <v>10</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="R13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S13" s="1">
+      <c r="S13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T13" s="1">
         <v>10000</v>
       </c>
-      <c r="T13" s="1">
+      <c r="U13" s="1">
         <v>100</v>
       </c>
-      <c r="U13" s="1" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:21">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C15" s="1">
         <v>9</v>
       </c>
@@ -1939,25 +1993,25 @@
         <v>10</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="N15" s="1">
+        <v>10</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P15" s="8" t="s">
         <v>31</v>
@@ -1968,17 +2022,17 @@
       <c r="R15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S15" s="1">
+      <c r="S15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T15" s="1">
         <v>10000</v>
       </c>
-      <c r="T15" s="1">
+      <c r="U15" s="1">
         <v>100</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:21">
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="C16" s="1">
         <v>10</v>
       </c>
@@ -1998,44 +2052,47 @@
         <v>10</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="N16" s="1">
+        <v>10</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S16" s="1">
+      <c r="S16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T16" s="1">
         <v>10000</v>
       </c>
-      <c r="T16" s="1">
+      <c r="U16" s="1">
         <v>100</v>
       </c>
-      <c r="U16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C17" s="1">
         <v>11</v>
       </c>
@@ -2055,44 +2112,47 @@
         <v>10</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N17" s="1">
+        <v>10</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S17" s="1">
+      <c r="S17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T17" s="1">
         <v>10000</v>
       </c>
-      <c r="T17" s="1">
+      <c r="U17" s="1">
         <v>100</v>
       </c>
-      <c r="U17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C18" s="1">
         <v>12</v>
       </c>
@@ -2112,44 +2172,47 @@
         <v>10</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N18" s="1">
+        <v>10</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="R18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S18" s="1">
+      <c r="S18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T18" s="1">
         <v>10000</v>
       </c>
-      <c r="T18" s="1">
+      <c r="U18" s="1">
         <v>100</v>
       </c>
-      <c r="U18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C19" s="1">
         <v>13</v>
       </c>
@@ -2169,44 +2232,47 @@
         <v>10</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N19" s="1">
+        <v>10</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="R19" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S19" s="1">
+      <c r="S19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T19" s="1">
         <v>10000</v>
       </c>
-      <c r="T19" s="1">
+      <c r="U19" s="1">
         <v>100</v>
       </c>
-      <c r="U19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C20" s="1">
         <v>14</v>
       </c>
@@ -2226,44 +2292,47 @@
         <v>10</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N20" s="1">
+        <v>10</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="R20" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S20" s="1">
+      <c r="S20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T20" s="1">
         <v>10000</v>
       </c>
-      <c r="T20" s="1">
+      <c r="U20" s="1">
         <v>100</v>
       </c>
-      <c r="U20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C21" s="1">
         <v>15</v>
       </c>
@@ -2283,44 +2352,47 @@
         <v>10</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J21" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="K21" s="8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" s="1">
+        <v>10</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q21" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="M21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="R21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S21" s="1">
+      <c r="S21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T21" s="1">
         <v>10000</v>
       </c>
-      <c r="T21" s="1">
+      <c r="U21" s="1">
         <v>100</v>
       </c>
-      <c r="U21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C22" s="1">
         <v>16</v>
       </c>
@@ -2340,52 +2412,55 @@
         <v>10</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N22" s="1">
+        <v>10</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="R22" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S22" s="1">
+      <c r="S22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T22" s="1">
         <v>10000</v>
       </c>
-      <c r="T22" s="1">
+      <c r="U22" s="1">
         <v>100</v>
       </c>
-      <c r="U22" s="4"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:21">
-      <c r="P23" s="3"/>
+      <c r="V22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="U23" s="3"/>
+      <c r="V23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C24" s="1">
         <v>17</v>
       </c>
@@ -2405,25 +2480,25 @@
         <v>10</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="N24" s="1">
+        <v>10</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="P24" s="8" t="s">
         <v>31</v>
@@ -2434,15 +2509,18 @@
       <c r="R24" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S24" s="1">
+      <c r="S24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T24" s="1">
         <v>10000</v>
       </c>
-      <c r="T24" s="1">
+      <c r="U24" s="1">
         <v>100</v>
       </c>
-      <c r="U24" s="4"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C25" s="1">
         <v>18</v>
       </c>
@@ -2462,44 +2540,47 @@
         <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="N25" s="1">
+        <v>10</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S25" s="1">
+      <c r="S25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T25" s="1">
         <v>10000</v>
       </c>
-      <c r="T25" s="1">
+      <c r="U25" s="1">
         <v>100</v>
       </c>
-      <c r="U25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C26" s="1">
         <v>19</v>
       </c>
@@ -2519,44 +2600,47 @@
         <v>10</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N26" s="1">
+        <v>10</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S26" s="1">
+      <c r="S26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T26" s="1">
         <v>10000</v>
       </c>
-      <c r="T26" s="1">
+      <c r="U26" s="1">
         <v>100</v>
       </c>
-      <c r="U26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C27" s="1">
         <v>20</v>
       </c>
@@ -2576,44 +2660,47 @@
         <v>10</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N27" s="1">
+        <v>10</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="R27" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S27" s="1">
+      <c r="S27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T27" s="1">
         <v>10000</v>
       </c>
-      <c r="T27" s="1">
+      <c r="U27" s="1">
         <v>100</v>
       </c>
-      <c r="U27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C28" s="1">
         <v>21</v>
       </c>
@@ -2633,44 +2720,47 @@
         <v>10</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N28" s="1">
+        <v>10</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="R28" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S28" s="1">
+      <c r="S28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T28" s="1">
         <v>10000</v>
       </c>
-      <c r="T28" s="1">
+      <c r="U28" s="1">
         <v>100</v>
       </c>
-      <c r="U28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V28" s="4"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C29" s="1">
         <v>22</v>
       </c>
@@ -2690,44 +2780,47 @@
         <v>10</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N29" s="1">
+        <v>10</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="R29" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S29" s="1">
+      <c r="S29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T29" s="1">
         <v>10000</v>
       </c>
-      <c r="T29" s="1">
+      <c r="U29" s="1">
         <v>100</v>
       </c>
-      <c r="U29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C30" s="1">
         <v>23</v>
       </c>
@@ -2747,44 +2840,47 @@
         <v>10</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N30" s="1">
+        <v>10</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="R30" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S30" s="1">
+      <c r="S30" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T30" s="1">
         <v>10000</v>
       </c>
-      <c r="T30" s="1">
+      <c r="U30" s="1">
         <v>100</v>
       </c>
-      <c r="U30" s="4"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="V30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="C31" s="1">
         <v>24</v>
       </c>
@@ -2804,54 +2900,57 @@
         <v>10</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="N31" s="1">
+        <v>10</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="R31" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S31" s="1">
+      <c r="S31" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T31" s="1">
         <v>10000</v>
       </c>
-      <c r="T31" s="1">
+      <c r="U31" s="1">
         <v>100</v>
       </c>
-      <c r="U31" s="4"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:21">
-      <c r="P32" s="3"/>
+      <c r="V31" s="4"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:22">
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="4"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/LegacyConfig.xlsx
+++ b/Excel/LegacyConfig.xlsx
@@ -1981,7 +1981,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F15" s="1">
         <v>6000003</v>
@@ -2040,7 +2040,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F16" s="1">
         <v>6000003</v>
@@ -2100,7 +2100,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F17" s="1">
         <v>6000003</v>
@@ -2160,7 +2160,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1">
         <v>6000003</v>
@@ -2220,7 +2220,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1">
         <v>6000003</v>
@@ -2280,7 +2280,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F20" s="1">
         <v>6000003</v>
@@ -2340,7 +2340,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="1">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F21" s="1">
         <v>6000003</v>
@@ -2400,7 +2400,7 @@
         <v>2</v>
       </c>
       <c r="E22" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1">
         <v>6000003</v>
@@ -2468,7 +2468,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1">
         <v>6000003</v>
@@ -2528,7 +2528,7 @@
         <v>3</v>
       </c>
       <c r="E25" s="1">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F25" s="1">
         <v>6000003</v>
@@ -2588,7 +2588,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="1">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F26" s="1">
         <v>6000003</v>
@@ -2648,7 +2648,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1">
         <v>6000003</v>
@@ -2708,7 +2708,7 @@
         <v>3</v>
       </c>
       <c r="E28" s="1">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F28" s="1">
         <v>6000003</v>
@@ -2768,7 +2768,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="1">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F29" s="1">
         <v>6000003</v>
@@ -2828,7 +2828,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="1">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F30" s="1">
         <v>6000003</v>
@@ -2888,7 +2888,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="1">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1">
         <v>6000003</v>

--- a/Excel/LegacyConfig.xlsx
+++ b/Excel/LegacyConfig.xlsx
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="87">
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="59">
   <si>
     <t>ID</t>
   </si>
@@ -41,7 +38,7 @@
     <t>Part</t>
   </si>
   <si>
-    <t>ItemId</t>
+    <t>KeyId</t>
   </si>
   <si>
     <t>StartLevel</t>
@@ -59,31 +56,16 @@
     <t>AtrVueList</t>
   </si>
   <si>
+    <t>RequireList</t>
+  </si>
+  <si>
     <t>SpeIdList</t>
   </si>
   <si>
     <t>SpeVueList</t>
   </si>
   <si>
-    <t>SpeLayerList</t>
-  </si>
-  <si>
-    <t>LevelIdList</t>
-  </si>
-  <si>
-    <t>LevelValueList</t>
-  </si>
-  <si>
-    <t>SpeAtrList</t>
-  </si>
-  <si>
-    <t>SpeLevel</t>
-  </si>
-  <si>
-    <t>Fee1</t>
-  </si>
-  <si>
-    <t>Fee2</t>
+    <t>SpeRequireList</t>
   </si>
   <si>
     <t>Id</t>
@@ -98,12 +80,6 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>long[]</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
     <t>传世战刃</t>
   </si>
   <si>
@@ -113,114 +89,66 @@
     <t>200,5</t>
   </si>
   <si>
+    <t>0,0,10,20</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
     <t>200</t>
   </si>
   <si>
-    <t>1003,4</t>
-  </si>
-  <si>
-    <t>5,200</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>传世战甲</t>
+  </si>
+  <si>
+    <t>2,1004</t>
+  </si>
+  <si>
+    <t>传世战链</t>
+  </si>
+  <si>
+    <t>100,2</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>传世战盔</t>
+  </si>
+  <si>
+    <t>1,1004</t>
+  </si>
+  <si>
+    <t>2000,2</t>
+  </si>
+  <si>
+    <t>传世战镯</t>
+  </si>
+  <si>
+    <t>传世战戒</t>
+  </si>
+  <si>
+    <t>传世战带</t>
+  </si>
+  <si>
+    <t>传世战靴</t>
+  </si>
+  <si>
+    <t>传世法杖</t>
+  </si>
+  <si>
+    <t>3,1005</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>传世战甲</t>
-  </si>
-  <si>
-    <t>2,1004</t>
-  </si>
-  <si>
-    <t>1002,4</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>传世战链</t>
-  </si>
-  <si>
-    <t>100,2</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>2,100</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>传世战盔</t>
-  </si>
-  <si>
-    <t>1,1004</t>
-  </si>
-  <si>
-    <t>2000,2</t>
-  </si>
-  <si>
-    <t>1001,4</t>
-  </si>
-  <si>
-    <t>5,100</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>传世战镯</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>传世战戒</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>传世战带</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>传世战靴</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>传世法杖</t>
-  </si>
-  <si>
-    <t>3,1005</t>
-  </si>
-  <si>
-    <t>1003,5</t>
-  </si>
-  <si>
     <t>传世法衣</t>
   </si>
   <si>
     <t>2,1005</t>
   </si>
   <si>
-    <t>1002,5</t>
-  </si>
-  <si>
     <t>传世法链</t>
   </si>
   <si>
@@ -230,9 +158,6 @@
     <t>1,1005</t>
   </si>
   <si>
-    <t>1001,5</t>
-  </si>
-  <si>
     <t>传世法镯</t>
   </si>
   <si>
@@ -254,18 +179,12 @@
     <t>6</t>
   </si>
   <si>
-    <t>1003,6</t>
-  </si>
-  <si>
     <t>传世道袍</t>
   </si>
   <si>
     <t>2,1006</t>
   </si>
   <si>
-    <t>1002,6</t>
-  </si>
-  <si>
     <t>传世道链</t>
   </si>
   <si>
@@ -273,9 +192,6 @@
   </si>
   <si>
     <t>1,1006</t>
-  </si>
-  <si>
-    <t>1001,6</t>
   </si>
   <si>
     <t>传世道镯</t>
@@ -1253,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1263,303 +1179,221 @@
     <col min="9" max="9" width="12.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="13.375" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.375" style="2" customWidth="1"/>
-    <col min="13" max="14" width="11.125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="15.625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="13" style="3" customWidth="1"/>
-    <col min="18" max="18" width="12" style="3" customWidth="1"/>
-    <col min="19" max="19" width="10.4166666666667" style="3" customWidth="1"/>
-    <col min="20" max="21" width="11.75" style="3" customWidth="1"/>
-    <col min="22" max="22" width="10.5" style="4" customWidth="1"/>
-    <col min="23" max="16371" width="9" style="2"/>
-    <col min="16372" max="16384" width="9" style="1"/>
+    <col min="12" max="12" width="16.5833333333333" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.5833333333333" style="2" customWidth="1"/>
+    <col min="14" max="15" width="11.125" style="2" customWidth="1"/>
+    <col min="16" max="17" width="11.75" style="3" customWidth="1"/>
+    <col min="18" max="18" width="10.5" style="4" customWidth="1"/>
+    <col min="19" max="16367" width="9" style="2"/>
+    <col min="16368" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:22">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="L1" s="3"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="R1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="L2" s="3"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
+      <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="R2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="M3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="V3" s="6"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="M4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="V4" s="6"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>10</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="N6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="T5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="U5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="V5" s="6"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>6000001</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7">
-        <v>10</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="1">
-        <v>10</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T6" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U6" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="O6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1570,7 +1404,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="1">
-        <v>6000002</v>
+        <v>2</v>
       </c>
       <c r="G7" s="7">
         <v>1</v>
@@ -1579,46 +1413,28 @@
         <v>10</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="1">
-        <v>10</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T7" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U7" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:22">
+        <v>21</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1629,7 +1445,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>6000003</v>
+        <v>3</v>
       </c>
       <c r="G8" s="7">
         <v>1</v>
@@ -1638,46 +1454,28 @@
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="L8" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="1">
-        <v>10</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U8" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:22">
+        <v>21</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1688,7 +1486,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="1">
-        <v>6000003</v>
+        <v>4</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
@@ -1697,46 +1495,28 @@
         <v>10</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="1">
-        <v>10</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T9" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U9" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:22">
+        <v>21</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1747,7 +1527,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="1">
-        <v>6000003</v>
+        <v>5</v>
       </c>
       <c r="G10" s="7">
         <v>1</v>
@@ -1756,46 +1536,28 @@
         <v>10</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" s="1">
-        <v>10</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T10" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U10" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:22">
+        <v>21</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1806,7 +1568,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1">
-        <v>6000003</v>
+        <v>6</v>
       </c>
       <c r="G11" s="7">
         <v>1</v>
@@ -1815,46 +1577,28 @@
         <v>10</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="J11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="L11" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" s="1">
-        <v>10</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T11" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U11" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:22">
+        <v>21</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1865,7 +1609,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="1">
-        <v>6000003</v>
+        <v>7</v>
       </c>
       <c r="G12" s="7">
         <v>1</v>
@@ -1874,46 +1618,28 @@
         <v>10</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12" s="1">
-        <v>10</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T12" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U12" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:22">
+        <v>21</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1924,7 +1650,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="1">
-        <v>6000003</v>
+        <v>8</v>
       </c>
       <c r="G13" s="7">
         <v>1</v>
@@ -1933,47 +1659,29 @@
         <v>10</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N13" s="1">
-        <v>10</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T13" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U13" s="1">
-        <v>100</v>
+        <v>21</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:22">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C15" s="1">
         <v>9</v>
       </c>
@@ -1984,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <v>6000003</v>
+        <v>9</v>
       </c>
       <c r="G15" s="7">
         <v>1</v>
@@ -1993,46 +1701,28 @@
         <v>10</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N15" s="1">
-        <v>10</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T15" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U15" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:22">
+        <v>37</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C16" s="1">
         <v>10</v>
       </c>
@@ -2043,7 +1733,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="1">
-        <v>6000003</v>
+        <v>10</v>
       </c>
       <c r="G16" s="7">
         <v>1</v>
@@ -2052,47 +1742,31 @@
         <v>10</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1">
-        <v>10</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T16" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U16" s="1">
-        <v>100</v>
-      </c>
-      <c r="V16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>37</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O16" s="1">
+        <v>10</v>
+      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C17" s="1">
         <v>11</v>
       </c>
@@ -2103,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="1">
-        <v>6000003</v>
+        <v>11</v>
       </c>
       <c r="G17" s="7">
         <v>1</v>
@@ -2112,47 +1786,31 @@
         <v>10</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N17" s="1">
-        <v>10</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T17" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U17" s="1">
-        <v>100</v>
-      </c>
-      <c r="V17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>37</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="1">
+        <v>10</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C18" s="1">
         <v>12</v>
       </c>
@@ -2163,7 +1821,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="1">
-        <v>6000003</v>
+        <v>12</v>
       </c>
       <c r="G18" s="7">
         <v>1</v>
@@ -2172,47 +1830,31 @@
         <v>10</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N18" s="1">
-        <v>10</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T18" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U18" s="1">
-        <v>100</v>
-      </c>
-      <c r="V18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>37</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" s="1">
+        <v>10</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C19" s="1">
         <v>13</v>
       </c>
@@ -2223,7 +1865,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="1">
-        <v>6000003</v>
+        <v>13</v>
       </c>
       <c r="G19" s="7">
         <v>1</v>
@@ -2232,47 +1874,31 @@
         <v>10</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N19" s="1">
-        <v>10</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="P19" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="R19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S19" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T19" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U19" s="1">
-        <v>100</v>
-      </c>
-      <c r="V19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>37</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="1">
+        <v>10</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C20" s="1">
         <v>14</v>
       </c>
@@ -2283,7 +1909,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="1">
-        <v>6000003</v>
+        <v>14</v>
       </c>
       <c r="G20" s="7">
         <v>1</v>
@@ -2292,47 +1918,31 @@
         <v>10</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N20" s="1">
-        <v>10</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T20" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U20" s="1">
-        <v>100</v>
-      </c>
-      <c r="V20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>37</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="1">
+        <v>10</v>
+      </c>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C21" s="1">
         <v>15</v>
       </c>
@@ -2343,7 +1953,7 @@
         <v>7</v>
       </c>
       <c r="F21" s="1">
-        <v>6000003</v>
+        <v>15</v>
       </c>
       <c r="G21" s="7">
         <v>1</v>
@@ -2352,47 +1962,31 @@
         <v>10</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N21" s="1">
-        <v>10</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="R21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T21" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U21" s="1">
-        <v>100</v>
-      </c>
-      <c r="V21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>37</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="1">
+        <v>10</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C22" s="1">
         <v>16</v>
       </c>
@@ -2403,7 +1997,7 @@
         <v>8</v>
       </c>
       <c r="F22" s="1">
-        <v>6000003</v>
+        <v>16</v>
       </c>
       <c r="G22" s="7">
         <v>1</v>
@@ -2412,55 +2006,37 @@
         <v>10</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N22" s="1">
-        <v>10</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T22" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U22" s="1">
-        <v>100</v>
-      </c>
-      <c r="V22" s="4"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>37</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="1">
+        <v>10</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="L23" s="3"/>
+      <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:22">
+      <c r="R23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C24" s="1">
         <v>17</v>
       </c>
@@ -2471,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>6000003</v>
+        <v>17</v>
       </c>
       <c r="G24" s="7">
         <v>1</v>
@@ -2480,47 +2056,31 @@
         <v>10</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N24" s="1">
-        <v>10</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T24" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U24" s="1">
-        <v>100</v>
-      </c>
-      <c r="V24" s="4"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>49</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O24" s="1">
+        <v>10</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C25" s="1">
         <v>18</v>
       </c>
@@ -2531,7 +2091,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="1">
-        <v>6000003</v>
+        <v>18</v>
       </c>
       <c r="G25" s="7">
         <v>1</v>
@@ -2540,47 +2100,31 @@
         <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N25" s="1">
-        <v>10</v>
-      </c>
-      <c r="O25" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q25" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R25" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T25" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U25" s="1">
-        <v>100</v>
-      </c>
-      <c r="V25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>49</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O25" s="1">
+        <v>10</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C26" s="1">
         <v>19</v>
       </c>
@@ -2591,7 +2135,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="1">
-        <v>6000003</v>
+        <v>19</v>
       </c>
       <c r="G26" s="7">
         <v>1</v>
@@ -2600,47 +2144,31 @@
         <v>10</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N26" s="1">
-        <v>10</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="P26" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q26" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="R26" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S26" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T26" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U26" s="1">
-        <v>100</v>
-      </c>
-      <c r="V26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>49</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="1">
+        <v>10</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C27" s="1">
         <v>20</v>
       </c>
@@ -2651,7 +2179,7 @@
         <v>4</v>
       </c>
       <c r="F27" s="1">
-        <v>6000003</v>
+        <v>20</v>
       </c>
       <c r="G27" s="7">
         <v>1</v>
@@ -2660,47 +2188,31 @@
         <v>10</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N27" s="1">
-        <v>10</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q27" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R27" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S27" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T27" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U27" s="1">
-        <v>100</v>
-      </c>
-      <c r="V27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:22">
+      <c r="N27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" s="1">
+        <v>10</v>
+      </c>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C28" s="1">
         <v>21</v>
       </c>
@@ -2711,7 +2223,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="1">
-        <v>6000003</v>
+        <v>21</v>
       </c>
       <c r="G28" s="7">
         <v>1</v>
@@ -2720,47 +2232,31 @@
         <v>10</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N28" s="1">
-        <v>10</v>
-      </c>
-      <c r="O28" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="R28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T28" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U28" s="1">
-        <v>100</v>
-      </c>
-      <c r="V28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>49</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28" s="1">
+        <v>10</v>
+      </c>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="4"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C29" s="1">
         <v>22</v>
       </c>
@@ -2771,7 +2267,7 @@
         <v>6</v>
       </c>
       <c r="F29" s="1">
-        <v>6000003</v>
+        <v>22</v>
       </c>
       <c r="G29" s="7">
         <v>1</v>
@@ -2780,47 +2276,31 @@
         <v>10</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N29" s="1">
-        <v>10</v>
-      </c>
-      <c r="O29" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="R29" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S29" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T29" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U29" s="1">
-        <v>100</v>
-      </c>
-      <c r="V29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>49</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29" s="1">
+        <v>10</v>
+      </c>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C30" s="1">
         <v>23</v>
       </c>
@@ -2831,7 +2311,7 @@
         <v>7</v>
       </c>
       <c r="F30" s="1">
-        <v>6000003</v>
+        <v>23</v>
       </c>
       <c r="G30" s="7">
         <v>1</v>
@@ -2840,47 +2320,31 @@
         <v>10</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N30" s="1">
-        <v>10</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="P30" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q30" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="R30" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T30" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U30" s="1">
-        <v>100</v>
-      </c>
-      <c r="V30" s="4"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>49</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" s="1">
+        <v>10</v>
+      </c>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C31" s="1">
         <v>24</v>
       </c>
@@ -2891,7 +2355,7 @@
         <v>8</v>
       </c>
       <c r="F31" s="1">
-        <v>6000003</v>
+        <v>24</v>
       </c>
       <c r="G31" s="7">
         <v>1</v>
@@ -2900,53 +2364,35 @@
         <v>10</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N31" s="1">
-        <v>10</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="P31" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q31" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="R31" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T31" s="1">
-        <v>10000</v>
-      </c>
-      <c r="U31" s="1">
-        <v>100</v>
-      </c>
-      <c r="V31" s="4"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:22">
+        <v>49</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31" s="1">
+        <v>10</v>
+      </c>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="4"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="L32" s="3"/>
+      <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="4"/>
+      <c r="R32" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/LegacyConfig.xlsx
+++ b/Excel/LegacyConfig.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="75">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
@@ -92,10 +95,16 @@
     <t>0,0,10,20</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>200</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>攻速</t>
   </si>
   <si>
     <t>传世战甲</t>
@@ -104,13 +113,25 @@
     <t>2,1004</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
     <t>传世战链</t>
   </si>
   <si>
     <t>100,2</t>
   </si>
   <si>
-    <t>100</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>冷却</t>
   </si>
   <si>
     <t>传世战盔</t>
@@ -122,27 +143,57 @@
     <t>2000,2</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
     <t>传世战镯</t>
   </si>
   <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
     <t>传世战戒</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
     <t>传世战带</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
     <t>传世战靴</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
     <t>传世法杖</t>
   </si>
   <si>
     <t>3,1005</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>传世法衣</t>
   </si>
   <si>
@@ -174,9 +225,6 @@
   </si>
   <si>
     <t>3,1006</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>传世道袍</t>
@@ -836,7 +884,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -849,6 +897,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1197,7 +1246,9 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="P1" s="3"/>
+      <c r="P1" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="Q1" s="3"/>
       <c r="R1" s="4"/>
     </row>
@@ -1210,7 +1261,9 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="3"/>
+      <c r="P2" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="4"/>
     </row>
@@ -1218,43 +1271,43 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
@@ -1264,43 +1317,43 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
@@ -1310,43 +1363,43 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
@@ -1372,25 +1425,28 @@
         <v>10</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="J6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="K6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="L6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="M6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="1">
-        <v>10</v>
+      <c r="N6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:18">
@@ -1413,25 +1469,28 @@
         <v>10</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O7" s="1">
-        <v>10</v>
+      <c r="P7" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:18">
@@ -1454,25 +1513,28 @@
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="N8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="1">
-        <v>10</v>
+      <c r="M8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:18">
@@ -1495,25 +1557,28 @@
         <v>10</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="1">
-        <v>10</v>
+      <c r="O9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:18">
@@ -1536,25 +1601,28 @@
         <v>10</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="N10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" s="1">
-        <v>10</v>
+      <c r="M10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:18">
@@ -1577,25 +1645,28 @@
         <v>10</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="8" t="s">
+      <c r="L11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" s="1">
-        <v>10</v>
+      <c r="M11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:18">
@@ -1618,25 +1689,28 @@
         <v>10</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="O12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O12" s="1">
-        <v>10</v>
+      <c r="P12" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:18">
@@ -1659,28 +1733,36 @@
         <v>10</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1"/>
+      <c r="O13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="M14" s="8"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="8"/>
+    </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C15" s="1">
         <v>9</v>
@@ -1701,25 +1783,28 @@
         <v>10</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="N15" s="8" t="s">
+      <c r="L15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="1">
-        <v>10</v>
+      <c r="N15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:18">
@@ -1742,27 +1827,29 @@
         <v>10</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M16" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O16" s="1">
-        <v>10</v>
-      </c>
-      <c r="P16" s="1"/>
+      <c r="L16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="Q16" s="1"/>
       <c r="R16" s="4"/>
     </row>
@@ -1786,27 +1873,29 @@
         <v>10</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" s="1">
-        <v>10</v>
-      </c>
-      <c r="P17" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="4"/>
     </row>
@@ -1830,27 +1919,29 @@
         <v>10</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="1">
-        <v>10</v>
-      </c>
-      <c r="P18" s="1"/>
+      <c r="L18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="4"/>
     </row>
@@ -1874,27 +1965,29 @@
         <v>10</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="1">
-        <v>10</v>
-      </c>
-      <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="4"/>
     </row>
@@ -1918,27 +2011,29 @@
         <v>10</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="J20" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="1">
-        <v>10</v>
-      </c>
-      <c r="P20" s="1"/>
+      <c r="N20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="4"/>
     </row>
@@ -1962,27 +2057,29 @@
         <v>10</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" s="1">
-        <v>10</v>
-      </c>
-      <c r="P21" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="4"/>
     </row>
@@ -2006,27 +2103,29 @@
         <v>10</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M22" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N22" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O22" s="1">
-        <v>10</v>
-      </c>
-      <c r="P22" s="1"/>
+      <c r="L22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="4"/>
     </row>
@@ -2056,27 +2155,29 @@
         <v>10</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M24" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N24" s="8" t="s">
+      <c r="L24" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="O24" s="1">
-        <v>10</v>
-      </c>
-      <c r="P24" s="1"/>
+      <c r="N24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="4"/>
     </row>
@@ -2100,27 +2201,29 @@
         <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K25" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M25" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O25" s="1">
-        <v>10</v>
-      </c>
-      <c r="P25" s="1"/>
+      <c r="L25" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="4"/>
     </row>
@@ -2144,27 +2247,29 @@
         <v>10</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="1">
-        <v>10</v>
-      </c>
-      <c r="P26" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="4"/>
     </row>
@@ -2188,27 +2293,29 @@
         <v>10</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O27" s="1">
-        <v>10</v>
-      </c>
-      <c r="P27" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="Q27" s="1"/>
       <c r="R27" s="4"/>
     </row>
@@ -2232,27 +2339,29 @@
         <v>10</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O28" s="1">
-        <v>10</v>
-      </c>
-      <c r="P28" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="4"/>
     </row>
@@ -2276,27 +2385,29 @@
         <v>10</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O29" s="1">
-        <v>10</v>
-      </c>
-      <c r="P29" s="1"/>
+        <v>72</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="4"/>
     </row>
@@ -2320,27 +2431,29 @@
         <v>10</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M30" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N30" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O30" s="1">
-        <v>10</v>
-      </c>
-      <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="4"/>
     </row>
@@ -2364,27 +2477,29 @@
         <v>10</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O31" s="1">
-        <v>10</v>
-      </c>
-      <c r="P31" s="1"/>
+        <v>74</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="Q31" s="1"/>
       <c r="R31" s="4"/>
     </row>

--- a/Excel/LegacyConfig.xlsx
+++ b/Excel/LegacyConfig.xlsx
@@ -884,7 +884,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -897,7 +897,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1422,27 +1421,27 @@
         <v>1</v>
       </c>
       <c r="H6" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P6" s="1" t="s">
@@ -1466,27 +1465,27 @@
         <v>1</v>
       </c>
       <c r="H7" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="N7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P7" s="1" t="s">
@@ -1510,27 +1509,27 @@
         <v>1</v>
       </c>
       <c r="H8" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="N8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="O8" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P8" s="1" t="s">
@@ -1554,27 +1553,27 @@
         <v>1</v>
       </c>
       <c r="H9" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="N9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="O9" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P9" s="1" t="s">
@@ -1598,27 +1597,27 @@
         <v>1</v>
       </c>
       <c r="H10" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="O10" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P10" s="1" t="s">
@@ -1642,27 +1641,27 @@
         <v>1</v>
       </c>
       <c r="H11" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="M11" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="N11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="O11" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P11" s="1" t="s">
@@ -1686,27 +1685,27 @@
         <v>1</v>
       </c>
       <c r="H12" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P12" s="1" t="s">
@@ -1730,39 +1729,34 @@
         <v>1</v>
       </c>
       <c r="H13" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="N13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="M14" s="8"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="8"/>
-    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1"/>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C15" s="1">
         <v>9</v>
@@ -1780,27 +1774,27 @@
         <v>1</v>
       </c>
       <c r="H15" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="K15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="N15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O15" s="9" t="s">
+      <c r="O15" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P15" s="1" t="s">
@@ -1824,27 +1818,27 @@
         <v>1</v>
       </c>
       <c r="H16" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="K16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="L16" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="M16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="N16" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O16" s="9" t="s">
+      <c r="O16" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P16" s="1" t="s">
@@ -1870,27 +1864,27 @@
         <v>1</v>
       </c>
       <c r="H17" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="M17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="N17" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O17" s="9" t="s">
+      <c r="O17" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P17" s="1" t="s">
@@ -1916,27 +1910,27 @@
         <v>1</v>
       </c>
       <c r="H18" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="M18" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="N18" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="9" t="s">
+      <c r="O18" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P18" s="1" t="s">
@@ -1962,27 +1956,27 @@
         <v>1</v>
       </c>
       <c r="H19" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="K19" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="L19" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="M19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="N19" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O19" s="9" t="s">
+      <c r="O19" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P19" s="1" t="s">
@@ -2008,27 +2002,27 @@
         <v>1</v>
       </c>
       <c r="H20" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="M20" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="N20" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O20" s="9" t="s">
+      <c r="O20" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P20" s="1" t="s">
@@ -2054,27 +2048,27 @@
         <v>1</v>
       </c>
       <c r="H21" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="K21" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="M21" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="N21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="O21" s="9" t="s">
+      <c r="O21" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P21" s="1" t="s">
@@ -2100,27 +2094,27 @@
         <v>1</v>
       </c>
       <c r="H22" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="M22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="N22" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O22" s="9" t="s">
+      <c r="O22" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P22" s="1" t="s">
@@ -2152,27 +2146,27 @@
         <v>1</v>
       </c>
       <c r="H24" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="L24" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M24" s="9" t="s">
+      <c r="M24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="N24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O24" s="9" t="s">
+      <c r="O24" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P24" s="1" t="s">
@@ -2198,27 +2192,27 @@
         <v>1</v>
       </c>
       <c r="H25" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="J25" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K25" s="9" t="s">
+      <c r="K25" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="L25" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M25" s="9" t="s">
+      <c r="M25" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="N25" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O25" s="9" t="s">
+      <c r="O25" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P25" s="1" t="s">
@@ -2244,27 +2238,27 @@
         <v>1</v>
       </c>
       <c r="H26" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="L26" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="9" t="s">
+      <c r="M26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="N26" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O26" s="9" t="s">
+      <c r="O26" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P26" s="1" t="s">
@@ -2290,27 +2284,27 @@
         <v>1</v>
       </c>
       <c r="H27" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K27" s="9" t="s">
+      <c r="K27" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="L27" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M27" s="9" t="s">
+      <c r="M27" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="N27" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O27" s="9" t="s">
+      <c r="O27" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P27" s="1" t="s">
@@ -2336,27 +2330,27 @@
         <v>1</v>
       </c>
       <c r="H28" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="L28" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M28" s="9" t="s">
+      <c r="M28" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="N28" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O28" s="9" t="s">
+      <c r="O28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P28" s="1" t="s">
@@ -2382,27 +2376,27 @@
         <v>1</v>
       </c>
       <c r="H29" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K29" s="9" t="s">
+      <c r="K29" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L29" s="9" t="s">
+      <c r="L29" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="9" t="s">
+      <c r="M29" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="N29" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O29" s="9" t="s">
+      <c r="O29" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P29" s="1" t="s">
@@ -2428,27 +2422,27 @@
         <v>1</v>
       </c>
       <c r="H30" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K30" s="9" t="s">
+      <c r="K30" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="L30" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="9" t="s">
+      <c r="M30" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="N30" s="9" t="s">
+      <c r="N30" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="O30" s="9" t="s">
+      <c r="O30" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P30" s="1" t="s">
@@ -2474,27 +2468,27 @@
         <v>1</v>
       </c>
       <c r="H31" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K31" s="9" t="s">
+      <c r="K31" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="L31" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M31" s="9" t="s">
+      <c r="M31" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="N31" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O31" s="9" t="s">
+      <c r="O31" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P31" s="1" t="s">

--- a/Excel/LegacyConfig.xlsx
+++ b/Excel/LegacyConfig.xlsx
@@ -89,7 +89,7 @@
     <t>3,1004</t>
   </si>
   <si>
-    <t>200,5</t>
+    <t>200,2</t>
   </si>
   <si>
     <t>0,0,10,20</t>
@@ -125,7 +125,7 @@
     <t>传世战链</t>
   </si>
   <si>
-    <t>100,2</t>
+    <t>100,1</t>
   </si>
   <si>
     <t>10</t>

--- a/Excel/LegacyConfig.xlsx
+++ b/Excel/LegacyConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="71">
   <si>
     <t>#</t>
   </si>
@@ -101,7 +101,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>30</t>
+    <t>20</t>
   </si>
   <si>
     <t>攻速</t>
@@ -110,7 +110,7 @@
     <t>传世战甲</t>
   </si>
   <si>
-    <t>2,1004</t>
+    <t>2,1002</t>
   </si>
   <si>
     <t>14</t>
@@ -137,7 +137,7 @@
     <t>传世战盔</t>
   </si>
   <si>
-    <t>1,1004</t>
+    <t>1,1001</t>
   </si>
   <si>
     <t>2000,2</t>
@@ -197,18 +197,12 @@
     <t>传世法衣</t>
   </si>
   <si>
-    <t>2,1005</t>
-  </si>
-  <si>
     <t>传世法链</t>
   </si>
   <si>
     <t>传世法帽</t>
   </si>
   <si>
-    <t>1,1005</t>
-  </si>
-  <si>
     <t>传世法镯</t>
   </si>
   <si>
@@ -230,16 +224,10 @@
     <t>传世道袍</t>
   </si>
   <si>
-    <t>2,1006</t>
-  </si>
-  <si>
     <t>传世道链</t>
   </si>
   <si>
     <t>传世道冠</t>
-  </si>
-  <si>
-    <t>1,1006</t>
   </si>
   <si>
     <t>传世道镯</t>
@@ -1824,7 +1812,7 @@
         <v>55</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>20</v>
@@ -1867,7 +1855,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>54</v>
@@ -1913,10 +1901,10 @@
         <v>30</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>37</v>
@@ -1959,10 +1947,10 @@
         <v>30</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>37</v>
@@ -2005,7 +1993,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>54</v>
@@ -2051,10 +2039,10 @@
         <v>30</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>32</v>
@@ -2097,10 +2085,10 @@
         <v>30</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>37</v>
@@ -2149,10 +2137,10 @@
         <v>30</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>20</v>
@@ -2195,10 +2183,10 @@
         <v>30</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>20</v>
@@ -2241,10 +2229,10 @@
         <v>30</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>32</v>
@@ -2287,10 +2275,10 @@
         <v>30</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>37</v>
@@ -2333,10 +2321,10 @@
         <v>30</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>37</v>
@@ -2379,10 +2367,10 @@
         <v>30</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>32</v>
@@ -2425,10 +2413,10 @@
         <v>30</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>32</v>
@@ -2471,10 +2459,10 @@
         <v>30</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>37</v>
